--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107057</v>
+        <v>107062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Jennifer Gao, Denise Gunnarsson</t>
+          <t>Denise Gunnarsson, Jennifer Gao, Åsa Tengström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1576,7 +1576,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Denise Gunnarsson, Jennifer Gao, Åsa Tengström</t>
+          <t>Åsa Tengström, Jennifer Gao, Denise Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
